--- a/Result/profitability/8131.xlsx
+++ b/Result/profitability/8131.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4625</v>
+        <v>0.54875</v>
       </c>
       <c r="N2" t="n">
-        <v>11.71</v>
+        <v>12.955</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
       <c r="N3" t="n">
-        <v>12.54875</v>
+        <v>13.94125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.92</v>
       </c>
       <c r="M4" t="n">
-        <v>0.60375</v>
+        <v>0.6825</v>
       </c>
       <c r="N4" t="n">
-        <v>13.56</v>
+        <v>14.76375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5337499999999999</v>
+        <v>0.7175</v>
       </c>
       <c r="N5" t="n">
-        <v>11.78625</v>
+        <v>14.4325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.34</v>
       </c>
       <c r="M6" t="n">
-        <v>0.55375</v>
+        <v>0.5987499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>10.2925</v>
+        <v>11.0075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>0.38125</v>
+        <v>0.38875</v>
       </c>
       <c r="N7" t="n">
-        <v>9.15875</v>
+        <v>9.425000000000001</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.47</v>
       </c>
       <c r="M8" t="n">
-        <v>0.32625</v>
+        <v>0.3275</v>
       </c>
       <c r="N8" t="n">
-        <v>8.19875</v>
+        <v>8.209999999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8131</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3157</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2537</v>
+      </c>
+      <c r="E75" t="n">
+        <v>620</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.64</v>
+      </c>
+      <c r="G75" t="n">
+        <v>485</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.35%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>39</v>
+      </c>
+      <c r="J75" t="n">
+        <v>524</v>
+      </c>
+      <c r="K75" t="n">
+        <v>429</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>12.16</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.01041666666666674</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.08999999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.004603580562659859</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.94</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>21.17</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-13.83660130718954</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
